--- a/results/attitudes/Robustness/ablation_shuffled_roles.xlsx
+++ b/results/attitudes/Robustness/ablation_shuffled_roles.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -50,6 +50,27 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -425,41 +446,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>texts</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>observed kappa</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>shuffled mean</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>shuffled SD</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>shuffled 95% upper</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>observed - shuffled mean</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p (shuffled &gt;= observed)</t>
         </is>
@@ -468,129 +499,306 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
+          <t>without persona (PCPzero)</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
           <t>ChatGpt</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>31</v>
-      </c>
       <c r="C2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.08409999999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0679</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0221</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1155</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1908</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Llama</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1229</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0639</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.06279999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.0202</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8172</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Deepseek</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>31</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5195</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Mistral</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>31</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1084</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1472</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5475</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>with persona (PCP)</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>ChatGpt</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>31</v>
+      </c>
+      <c r="D7" t="n">
         <v>0.0233</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.0257</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0459</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="E7" t="n">
+        <v>0.0271</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0467</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.0998</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.5205</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="H7" t="n">
+        <v>-0.0038</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5425</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>Llama</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>31</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="C8" t="n">
+        <v>31</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>Gemini</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>31</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="C9" t="n">
+        <v>31</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>Deepseek</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>31</v>
-      </c>
-      <c r="C5" t="n">
+      <c r="C10" t="n">
+        <v>31</v>
+      </c>
+      <c r="D10" t="n">
         <v>0.0192</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.0215</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.0219</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.0604</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.4765</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="E10" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.4805</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>31</v>
-      </c>
-      <c r="C6" t="n">
+      <c r="C11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.016</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.0302</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.0721</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1473</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.5704</v>
+      <c r="E11" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1427</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.0094</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.5335</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A2:A6"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>